--- a/excel/template-contacts.xlsx
+++ b/excel/template-contacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\github\apiPOS-Official\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCF887E-15FF-4EA0-B02C-07843CE42167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398B25EA-7AC7-45E2-A5FA-961E9200B4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
